--- a/network/file/成绩登分册-4.xlsx
+++ b/network/file/成绩登分册-4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\network\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63E24DB-8857-4F4E-A2AA-0C6E5355F8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF21A86-A014-4C8A-9C79-719F378542DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1D86DE0-A88D-486A-A312-07EB4B609A42}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="179">
   <si>
     <t>广州华立学院学生平时成绩登记表</t>
   </si>
@@ -535,15 +535,39 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>其它活动</t>
-    <phoneticPr fontId="25" type="noConversion"/>
-  </si>
-  <si>
     <t>平均签到率</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>考试</t>
+    <t>考试成绩</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>作弊</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>全勤</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>平时考试</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>平时</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终成绩</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>表现OP</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +575,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -560,41 +584,48 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -602,6 +633,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -609,18 +641,21 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -628,6 +663,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -635,6 +671,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -642,6 +679,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -649,6 +687,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -656,12 +695,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -669,6 +710,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -676,40 +718,47 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -725,8 +774,36 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -916,18 +993,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1260,7 +1325,7 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1302,90 +1367,138 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="33" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1434,7 +1547,17 @@
     <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="注释" xfId="1" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1508,13 +1631,13 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStylePreset3_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{E584051D-1E60-4E94-8ADD-D63CF42CA6B9}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1789,218 +1912,316 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="5" customWidth="1"/>
     <col min="4" max="11" width="7.25" customWidth="1"/>
-    <col min="12" max="12" width="7.875" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="12" max="15" width="7.875" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+    </row>
+    <row r="2" spans="1:18" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34" t="s">
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34" t="s">
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34" t="s">
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="19"/>
-    </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="36" t="s">
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="40"/>
+    </row>
+    <row r="3" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="35" t="s">
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="52" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="36"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="31" t="s">
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="Q3" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="R3" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="59" t="s">
         <v>169</v>
       </c>
-      <c r="I4" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="35"/>
-    </row>
-    <row r="5" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="36"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="35"/>
-      <c r="N5" s="27" t="s">
+      <c r="K4" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L4" s="52"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+    </row>
+    <row r="5" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="59"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="Q5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="O5" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="31" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
+      <c r="E6" s="25">
+        <v>60</v>
+      </c>
+      <c r="F6" s="25">
+        <v>60</v>
+      </c>
+      <c r="G6" s="25">
+        <v>60</v>
+      </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L6" s="10">
+        <v>60</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>L6*0.3+R6*0.7</f>
+        <v>33.049999999999997</v>
+      </c>
+      <c r="R6" s="29">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="44" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="E7" s="25">
+        <v>60</v>
+      </c>
+      <c r="F7" s="25">
+        <v>60</v>
+      </c>
+      <c r="G7" s="25">
+        <v>60</v>
+      </c>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L7" s="10">
+        <v>90</v>
+      </c>
+      <c r="Q7" s="2">
+        <f t="shared" ref="Q7:Q49" si="0">L7*0.3+R7*0.7</f>
+        <v>60.25</v>
+      </c>
+      <c r="R7" s="29">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="31" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="E8" s="25">
+        <v>60</v>
+      </c>
+      <c r="F8" s="25">
+        <v>60</v>
+      </c>
+      <c r="G8" s="25">
+        <v>60</v>
+      </c>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="9" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L8" s="10">
+        <v>60</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q8" s="2">
+        <f t="shared" si="0"/>
+        <v>48.45</v>
+      </c>
+      <c r="R8" s="29">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="26" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="10">
+      <c r="E9" s="33">
         <v>56</v>
       </c>
-      <c r="F9" s="10"/>
+      <c r="F9" s="10">
+        <v>78</v>
+      </c>
       <c r="G9" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H9" s="10"/>
-      <c r="I9" s="10">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10">
+        <v>75.8</v>
+      </c>
+      <c r="M9" s="2">
+        <f>E9*0.3+F9*0.5+G9*0.2+J9+K9</f>
+        <v>75.8</v>
+      </c>
+      <c r="N9" s="2">
+        <f>O9+P9</f>
+        <v>129</v>
+      </c>
+      <c r="O9" s="2">
         <v>40</v>
       </c>
-      <c r="J9" s="10">
+      <c r="P9" s="2">
         <v>89</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q9" s="2">
+        <f t="shared" si="0"/>
+        <v>71.039999999999992</v>
+      </c>
+      <c r="R9" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
@@ -2014,21 +2235,44 @@
       <c r="E10" s="10">
         <v>100</v>
       </c>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10">
+        <v>87</v>
+      </c>
       <c r="G10" s="10">
         <v>83</v>
       </c>
       <c r="H10" s="10"/>
-      <c r="I10" s="10">
+      <c r="I10" s="10"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="10">
+        <v>5</v>
+      </c>
+      <c r="L10" s="10">
+        <v>95.1</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" ref="M10:M49" si="1">E10*0.3+F10*0.5+G10*0.2+J10+K10</f>
+        <v>95.1</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" ref="N10:N49" si="2">O10+P10</f>
         <v>54</v>
       </c>
-      <c r="J10" s="50">
+      <c r="O10" s="2">
+        <v>54</v>
+      </c>
+      <c r="P10" s="41">
         <v>0</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q10" s="2">
+        <f t="shared" si="0"/>
+        <v>64.22999999999999</v>
+      </c>
+      <c r="R10" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>40</v>
       </c>
@@ -2042,23 +2286,46 @@
       <c r="E11" s="10">
         <v>100</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="10">
+        <v>100</v>
+      </c>
       <c r="G11" s="10">
-        <v>83</v>
-      </c>
-      <c r="H11" s="10">
+        <v>100</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10">
         <v>2</v>
       </c>
-      <c r="I11" s="10">
+      <c r="K11" s="10">
+        <v>5</v>
+      </c>
+      <c r="L11" s="10">
+        <v>100</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+      <c r="O11" s="2">
         <v>94</v>
       </c>
-      <c r="J11" s="10">
+      <c r="P11" s="2">
         <v>88</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q11" s="2">
+        <f t="shared" si="0"/>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="R11" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>43</v>
       </c>
@@ -2072,77 +2339,144 @@
       <c r="E12" s="10">
         <v>100</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="10">
+        <v>100</v>
+      </c>
       <c r="G12" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="10">
+      <c r="I12" s="10"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="10">
+        <v>5</v>
+      </c>
+      <c r="L12" s="10">
+        <v>100</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="J12" s="50">
+      <c r="O12" s="2">
+        <v>62</v>
+      </c>
+      <c r="P12" s="41">
         <v>0</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q12" s="2">
+        <f t="shared" si="0"/>
+        <v>75.849999999999994</v>
+      </c>
+      <c r="R12" s="2">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="10"/>
-      <c r="E13" s="10">
+      <c r="E13" s="33">
         <v>44</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="10">
+        <v>80</v>
+      </c>
       <c r="G13" s="10">
         <v>83</v>
       </c>
       <c r="H13" s="10"/>
-      <c r="I13" s="10">
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="66">
+        <v>75</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="1"/>
+        <v>69.800000000000011</v>
+      </c>
+      <c r="N13" s="2">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="J13" s="10">
+      <c r="O13" s="2">
+        <v>10</v>
+      </c>
+      <c r="P13" s="2">
         <v>0</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q13" s="2">
+        <f t="shared" si="0"/>
+        <v>59.599999999999994</v>
+      </c>
+      <c r="R13" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="44" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10">
         <v>100</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="10">
+        <v>100</v>
+      </c>
       <c r="G14" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H14" s="10"/>
-      <c r="I14" s="10">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10">
+        <v>5</v>
+      </c>
+      <c r="L14" s="25">
+        <v>100</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="N14" s="2">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="O14" s="2">
         <v>62</v>
       </c>
-      <c r="J14" s="10">
+      <c r="P14" s="2">
         <v>98</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q14" s="2">
+        <f t="shared" si="0"/>
+        <v>60.8</v>
+      </c>
+      <c r="R14" s="29">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>52</v>
       </c>
@@ -2156,21 +2490,44 @@
       <c r="E15" s="10">
         <v>100</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="10">
+        <v>100</v>
+      </c>
       <c r="G15" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H15" s="10"/>
-      <c r="I15" s="10">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10">
+        <v>5</v>
+      </c>
+      <c r="L15" s="10">
+        <v>100</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+      <c r="O15" s="2">
         <v>70</v>
       </c>
-      <c r="J15" s="10">
+      <c r="P15" s="2">
         <v>65</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q15" s="2">
+        <f t="shared" si="0"/>
+        <v>68.849999999999994</v>
+      </c>
+      <c r="R15" s="2">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>55</v>
       </c>
@@ -2184,21 +2541,44 @@
       <c r="E16" s="10">
         <v>100</v>
       </c>
-      <c r="F16" s="10"/>
+      <c r="F16" s="10">
+        <v>85</v>
+      </c>
       <c r="G16" s="10">
         <v>83</v>
       </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="10">
+      <c r="I16" s="10"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="10">
+        <v>5</v>
+      </c>
+      <c r="L16" s="10">
+        <v>94.1</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="1"/>
+        <v>94.1</v>
+      </c>
+      <c r="N16" s="2">
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="J16" s="50">
+      <c r="O16" s="2">
+        <v>60</v>
+      </c>
+      <c r="P16" s="41">
         <v>0</v>
       </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q16" s="2">
+        <f t="shared" si="0"/>
+        <v>51.679999999999993</v>
+      </c>
+      <c r="R16" s="29">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>58</v>
       </c>
@@ -2212,23 +2592,46 @@
       <c r="E17" s="10">
         <v>100</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="10">
+        <v>88</v>
+      </c>
       <c r="G17" s="10">
         <v>83</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="25">
         <v>3</v>
       </c>
-      <c r="I17" s="10">
+      <c r="K17" s="10">
+        <v>5</v>
+      </c>
+      <c r="L17" s="10">
+        <v>98.6</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="1"/>
+        <v>98.6</v>
+      </c>
+      <c r="N17" s="2">
+        <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="J17" s="50">
+      <c r="O17" s="2">
+        <v>62</v>
+      </c>
+      <c r="P17" s="41">
         <v>0</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q17" s="2">
+        <f t="shared" si="0"/>
+        <v>72.63</v>
+      </c>
+      <c r="R17" s="2">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>61</v>
       </c>
@@ -2242,21 +2645,44 @@
       <c r="E18" s="10">
         <v>100</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="10">
+        <v>100</v>
+      </c>
       <c r="G18" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="10">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10">
+        <v>5</v>
+      </c>
+      <c r="L18" s="10">
+        <v>100</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="N18" s="2">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+      <c r="O18" s="2">
         <v>84</v>
       </c>
-      <c r="J18" s="10">
+      <c r="P18" s="2">
         <v>97</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q18" s="2">
+        <f t="shared" si="0"/>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="R18" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
         <v>64</v>
       </c>
@@ -2270,51 +2696,95 @@
       <c r="E19" s="10">
         <v>100</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="10">
+        <v>84</v>
+      </c>
       <c r="G19" s="10">
-        <v>83</v>
-      </c>
-      <c r="H19" s="10">
+        <v>92</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="10">
+      <c r="K19" s="10">
+        <v>5</v>
+      </c>
+      <c r="L19" s="10">
+        <v>96.4</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="1"/>
+        <v>96.4</v>
+      </c>
+      <c r="N19" s="2">
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="J19" s="10">
+      <c r="O19" s="2">
+        <v>92</v>
+      </c>
+      <c r="P19" s="2">
         <v>0</v>
       </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q19" s="2">
+        <f t="shared" si="0"/>
+        <v>75.819999999999993</v>
+      </c>
+      <c r="R19" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="44" t="s">
         <v>69</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10">
         <v>67</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="10">
+        <v>100</v>
+      </c>
       <c r="G20" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
-      <c r="I20" s="10">
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="25">
+        <v>90.1</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="1"/>
+        <v>90.1</v>
+      </c>
+      <c r="N20" s="2">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+      <c r="O20" s="2">
         <v>36</v>
       </c>
-      <c r="J20" s="10">
-        <v>100</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P20" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="2">
+        <f t="shared" si="0"/>
+        <v>61.33</v>
+      </c>
+      <c r="R20" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
         <v>70</v>
       </c>
@@ -2328,23 +2798,44 @@
       <c r="E21" s="10">
         <v>89</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="10">
+        <v>73</v>
+      </c>
       <c r="G21" s="10">
         <v>83</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="25">
         <v>1</v>
       </c>
-      <c r="I21" s="10">
+      <c r="K21" s="10"/>
+      <c r="L21" s="10">
+        <v>80.800000000000011</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="1"/>
+        <v>80.800000000000011</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="J21" s="50">
+      <c r="O21" s="2">
+        <v>38</v>
+      </c>
+      <c r="P21" s="41">
         <v>0</v>
       </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q21" s="2">
+        <f t="shared" si="0"/>
+        <v>60.29</v>
+      </c>
+      <c r="R21" s="2">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
         <v>73</v>
       </c>
@@ -2358,23 +2849,46 @@
       <c r="E22" s="10">
         <v>100</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="10">
+        <v>100</v>
+      </c>
       <c r="G22" s="10">
-        <v>83</v>
-      </c>
-      <c r="H22" s="10">
+        <v>100</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10">
         <v>2</v>
       </c>
-      <c r="I22" s="10">
+      <c r="K22" s="10">
+        <v>5</v>
+      </c>
+      <c r="L22" s="10">
+        <v>100</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+      <c r="O22" s="2">
         <v>66</v>
       </c>
-      <c r="J22" s="10">
+      <c r="P22" s="2">
         <v>99</v>
       </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q22" s="2">
+        <f t="shared" si="0"/>
+        <v>78.3</v>
+      </c>
+      <c r="R22" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
         <v>76</v>
       </c>
@@ -2388,21 +2902,44 @@
       <c r="E23" s="10">
         <v>100</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="10">
+        <v>80</v>
+      </c>
       <c r="G23" s="10">
         <v>83</v>
       </c>
       <c r="H23" s="10"/>
-      <c r="I23" s="10">
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10">
+        <v>5</v>
+      </c>
+      <c r="L23" s="10">
+        <v>91.6</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="1"/>
+        <v>91.6</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="J23" s="10">
+      <c r="O23" s="2">
+        <v>54</v>
+      </c>
+      <c r="P23" s="2">
         <v>0</v>
       </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q23" s="2">
+        <f t="shared" si="0"/>
+        <v>70.88</v>
+      </c>
+      <c r="R23" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
         <v>79</v>
       </c>
@@ -2414,23 +2951,44 @@
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10">
-        <v>67</v>
-      </c>
-      <c r="F24" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="F24" s="10">
+        <v>100</v>
+      </c>
       <c r="G24" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H24" s="10"/>
-      <c r="I24" s="10">
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10">
+        <v>92.2</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="1"/>
+        <v>92.2</v>
+      </c>
+      <c r="N24" s="2">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="O24" s="2">
         <v>26</v>
       </c>
-      <c r="J24" s="10">
+      <c r="P24" s="2">
         <v>99</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q24" s="2">
+        <f t="shared" si="0"/>
+        <v>79.11</v>
+      </c>
+      <c r="R24" s="2">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
         <v>82</v>
       </c>
@@ -2444,49 +3002,91 @@
       <c r="E25" s="10">
         <v>89</v>
       </c>
-      <c r="F25" s="10"/>
+      <c r="F25" s="10">
+        <v>100</v>
+      </c>
       <c r="G25" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H25" s="10"/>
-      <c r="I25" s="10">
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" si="1"/>
+        <v>96.7</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+      <c r="O25" s="2">
         <v>56</v>
       </c>
-      <c r="J25" s="10">
+      <c r="P25" s="2">
         <v>76</v>
       </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q25" s="2">
+        <f t="shared" si="0"/>
+        <v>71.709999999999994</v>
+      </c>
+      <c r="R25" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="26" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="10"/>
-      <c r="E26" s="10">
+      <c r="E26" s="33">
         <v>33</v>
       </c>
-      <c r="F26" s="10"/>
+      <c r="F26" s="10">
+        <v>100</v>
+      </c>
       <c r="G26" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H26" s="10"/>
-      <c r="I26" s="10">
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10">
+        <v>79.8</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="1"/>
+        <v>79.900000000000006</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="O26" s="2">
         <v>44</v>
       </c>
-      <c r="J26" s="10">
+      <c r="P26" s="2">
         <v>96</v>
       </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-    </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q26" s="2">
+        <f t="shared" si="0"/>
+        <v>70.489999999999995</v>
+      </c>
+      <c r="R26" s="2">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
         <v>88</v>
       </c>
@@ -2500,21 +3100,42 @@
       <c r="E27" s="10">
         <v>78</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="10">
+        <v>83</v>
+      </c>
       <c r="G27" s="10">
         <v>83</v>
       </c>
       <c r="H27" s="10"/>
-      <c r="I27" s="10">
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10">
+        <v>81.5</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="1"/>
+        <v>81.5</v>
+      </c>
+      <c r="N27" s="2">
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="J27" s="10">
+      <c r="O27" s="2">
+        <v>46</v>
+      </c>
+      <c r="P27" s="2">
         <v>0</v>
       </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q27" s="2">
+        <f t="shared" si="0"/>
+        <v>69.599999999999994</v>
+      </c>
+      <c r="R27" s="2">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
         <v>91</v>
       </c>
@@ -2528,77 +3149,142 @@
       <c r="E28" s="10">
         <v>100</v>
       </c>
-      <c r="F28" s="10"/>
+      <c r="F28" s="10">
+        <v>80</v>
+      </c>
       <c r="G28" s="10">
         <v>83</v>
       </c>
       <c r="H28" s="10"/>
-      <c r="I28" s="10">
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10">
+        <v>5</v>
+      </c>
+      <c r="L28" s="10">
+        <v>91.6</v>
+      </c>
+      <c r="M28" s="2">
+        <f t="shared" si="1"/>
+        <v>91.6</v>
+      </c>
+      <c r="N28" s="2">
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="J28" s="10">
+      <c r="O28" s="2">
+        <v>56</v>
+      </c>
+      <c r="P28" s="2">
         <v>0</v>
       </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q28" s="2">
+        <f t="shared" si="0"/>
+        <v>72.63</v>
+      </c>
+      <c r="R28" s="2">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="44" t="s">
         <v>96</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10">
         <v>89</v>
       </c>
-      <c r="F29" s="10"/>
+      <c r="F29" s="10">
+        <v>83</v>
+      </c>
       <c r="G29" s="10">
         <v>83</v>
       </c>
       <c r="H29" s="10"/>
-      <c r="I29" s="10">
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10">
+        <v>84.800000000000011</v>
+      </c>
+      <c r="M29" s="2">
+        <f t="shared" si="1"/>
+        <v>84.800000000000011</v>
+      </c>
+      <c r="N29" s="2">
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="J29" s="10">
+      <c r="O29" s="2">
+        <v>48</v>
+      </c>
+      <c r="P29" s="2">
         <v>0</v>
       </c>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q29" s="2">
+        <f t="shared" si="0"/>
+        <v>54.84</v>
+      </c>
+      <c r="R29" s="29">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="27" t="s">
         <v>99</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10">
         <v>56</v>
       </c>
-      <c r="F30" s="10"/>
+      <c r="F30" s="10">
+        <v>100</v>
+      </c>
       <c r="G30" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H30" s="10"/>
-      <c r="I30" s="10">
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10">
+        <v>86.8</v>
+      </c>
+      <c r="M30" s="2">
+        <f t="shared" si="1"/>
+        <v>86.8</v>
+      </c>
+      <c r="N30" s="2">
+        <f t="shared" si="2"/>
+        <v>126</v>
+      </c>
+      <c r="O30" s="2">
         <v>28</v>
       </c>
-      <c r="J30" s="10">
+      <c r="P30" s="2">
         <v>98</v>
       </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q30" s="2">
+        <f t="shared" si="0"/>
+        <v>70.84</v>
+      </c>
+      <c r="R30" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
         <v>100</v>
       </c>
@@ -2612,21 +3298,42 @@
       <c r="E31" s="10">
         <v>78</v>
       </c>
-      <c r="F31" s="10"/>
+      <c r="F31" s="10">
+        <v>80</v>
+      </c>
       <c r="G31" s="10">
         <v>83</v>
       </c>
       <c r="H31" s="10"/>
-      <c r="I31" s="10">
+      <c r="I31" s="10"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10">
+        <v>80</v>
+      </c>
+      <c r="M31" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N31" s="2">
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="J31" s="50">
+      <c r="O31" s="2">
+        <v>42</v>
+      </c>
+      <c r="P31" s="41">
         <v>0</v>
       </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q31" s="2">
+        <f t="shared" si="0"/>
+        <v>68.449999999999989</v>
+      </c>
+      <c r="R31" s="2">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>103</v>
       </c>
@@ -2640,23 +3347,46 @@
       <c r="E32" s="10">
         <v>100</v>
       </c>
-      <c r="F32" s="10"/>
+      <c r="F32" s="10">
+        <v>100</v>
+      </c>
       <c r="G32" s="10">
-        <v>83</v>
-      </c>
-      <c r="H32" s="10">
+        <v>100</v>
+      </c>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10">
         <v>1</v>
       </c>
-      <c r="I32" s="10">
+      <c r="K32" s="10">
+        <v>5</v>
+      </c>
+      <c r="L32" s="10">
+        <v>100</v>
+      </c>
+      <c r="M32" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="N32" s="2">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+      <c r="O32" s="2">
         <v>90</v>
       </c>
-      <c r="J32" s="10">
+      <c r="P32" s="2">
         <v>87</v>
       </c>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q32" s="2">
+        <f t="shared" si="0"/>
+        <v>81.8</v>
+      </c>
+      <c r="R32" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
         <v>106</v>
       </c>
@@ -2670,28 +3400,51 @@
       <c r="E33" s="10">
         <v>100</v>
       </c>
-      <c r="F33" s="10"/>
+      <c r="F33" s="10">
+        <v>81</v>
+      </c>
       <c r="G33" s="10">
         <v>83</v>
       </c>
       <c r="H33" s="10"/>
-      <c r="I33" s="10">
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10">
+        <v>5</v>
+      </c>
+      <c r="L33" s="10">
+        <v>92.1</v>
+      </c>
+      <c r="M33" s="2">
+        <f t="shared" si="1"/>
+        <v>92.1</v>
+      </c>
+      <c r="N33" s="2">
+        <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="J33" s="10">
+      <c r="O33" s="2">
+        <v>58</v>
+      </c>
+      <c r="P33" s="2">
         <v>0</v>
       </c>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q33" s="2">
+        <f t="shared" si="0"/>
+        <v>67.53</v>
+      </c>
+      <c r="R33" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="31" t="s">
         <v>111</v>
       </c>
       <c r="D34" s="10"/>
@@ -2702,13 +3455,18 @@
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
-      <c r="J34" s="50">
-        <v>0</v>
-      </c>
+      <c r="J34" s="25"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
-    </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N34" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
         <v>112</v>
       </c>
@@ -2722,79 +3480,144 @@
       <c r="E35" s="10">
         <v>100</v>
       </c>
-      <c r="F35" s="10"/>
+      <c r="F35" s="10">
+        <v>100</v>
+      </c>
       <c r="G35" s="10">
-        <v>83</v>
-      </c>
-      <c r="H35" s="10">
+        <v>100</v>
+      </c>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10">
         <v>1</v>
       </c>
-      <c r="I35" s="10">
+      <c r="K35" s="10">
+        <v>5</v>
+      </c>
+      <c r="L35" s="10">
+        <v>100</v>
+      </c>
+      <c r="M35" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="N35" s="2">
+        <f t="shared" si="2"/>
+        <v>117</v>
+      </c>
+      <c r="O35" s="2">
         <v>90</v>
       </c>
-      <c r="J35" s="10">
+      <c r="P35" s="2">
         <v>27</v>
       </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-    </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q35" s="2">
+        <f t="shared" si="0"/>
+        <v>67.099999999999994</v>
+      </c>
+      <c r="R35" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="26" t="s">
         <v>116</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="10"/>
-      <c r="E36" s="10">
+      <c r="E36" s="33">
         <v>44</v>
       </c>
-      <c r="F36" s="10"/>
+      <c r="F36" s="10">
+        <v>81</v>
+      </c>
       <c r="G36" s="10">
         <v>83</v>
       </c>
       <c r="H36" s="10"/>
-      <c r="I36" s="10">
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10">
+        <v>70.300000000000011</v>
+      </c>
+      <c r="M36" s="2">
+        <f t="shared" si="1"/>
+        <v>70.300000000000011</v>
+      </c>
+      <c r="N36" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J36" s="10">
+      <c r="O36" s="2">
         <v>0</v>
       </c>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P36" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2">
+        <f t="shared" si="0"/>
+        <v>53.64</v>
+      </c>
+      <c r="R36" s="2">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="26" t="s">
         <v>119</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D37" s="10"/>
-      <c r="E37" s="10">
+      <c r="E37" s="33">
         <v>56</v>
       </c>
-      <c r="F37" s="10"/>
+      <c r="F37" s="10">
+        <v>95</v>
+      </c>
       <c r="G37" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H37" s="10"/>
-      <c r="I37" s="10">
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10">
+        <v>84.3</v>
+      </c>
+      <c r="M37" s="2">
+        <f t="shared" si="1"/>
+        <v>84.3</v>
+      </c>
+      <c r="N37" s="2">
+        <f t="shared" si="2"/>
+        <v>111</v>
+      </c>
+      <c r="O37" s="2">
         <v>18</v>
       </c>
-      <c r="J37" s="10">
+      <c r="P37" s="2">
         <v>93</v>
       </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q37" s="2">
+        <f t="shared" si="0"/>
+        <v>55.39</v>
+      </c>
+      <c r="R37" s="29">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
         <v>121</v>
       </c>
@@ -2808,21 +3631,42 @@
       <c r="E38" s="10">
         <v>89</v>
       </c>
-      <c r="F38" s="10"/>
+      <c r="F38" s="10">
+        <v>100</v>
+      </c>
       <c r="G38" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H38" s="10"/>
-      <c r="I38" s="10">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="M38" s="2">
+        <f>E38*0.3+F38*0.5+G38*0.2+J38+K38</f>
+        <v>96.7</v>
+      </c>
+      <c r="N38" s="2">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="O38" s="2">
         <v>78</v>
       </c>
-      <c r="J38" s="10">
+      <c r="P38" s="2">
         <v>98</v>
       </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q38" s="2">
+        <f t="shared" si="0"/>
+        <v>73.81</v>
+      </c>
+      <c r="R38" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
         <v>124</v>
       </c>
@@ -2836,23 +3680,46 @@
       <c r="E39" s="10">
         <v>100</v>
       </c>
-      <c r="F39" s="10"/>
+      <c r="F39" s="10">
+        <v>100</v>
+      </c>
       <c r="G39" s="10">
-        <v>83</v>
-      </c>
-      <c r="H39" s="10">
+        <v>100</v>
+      </c>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10">
         <v>1</v>
       </c>
-      <c r="I39" s="10">
+      <c r="K39" s="10">
+        <v>5</v>
+      </c>
+      <c r="L39" s="10">
+        <v>100</v>
+      </c>
+      <c r="M39" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="N39" s="2">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+      <c r="O39" s="2">
         <v>86</v>
       </c>
-      <c r="J39" s="10">
+      <c r="P39" s="2">
         <v>92</v>
       </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q39" s="2">
+        <f t="shared" si="0"/>
+        <v>90.9</v>
+      </c>
+      <c r="R39" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="7" t="s">
         <v>127</v>
       </c>
@@ -2866,21 +3733,42 @@
       <c r="E40" s="10">
         <v>89</v>
       </c>
-      <c r="F40" s="10"/>
+      <c r="F40" s="10">
+        <v>100</v>
+      </c>
       <c r="G40" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H40" s="10"/>
-      <c r="I40" s="10">
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="M40" s="2">
+        <f t="shared" si="1"/>
+        <v>96.7</v>
+      </c>
+      <c r="N40" s="2">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+      <c r="O40" s="2">
         <v>66</v>
       </c>
-      <c r="J40" s="10">
+      <c r="P40" s="2">
         <v>92</v>
       </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q40" s="2">
+        <f t="shared" si="0"/>
+        <v>73.109999999999985</v>
+      </c>
+      <c r="R40" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7" t="s">
         <v>130</v>
       </c>
@@ -2894,21 +3782,42 @@
       <c r="E41" s="10">
         <v>67</v>
       </c>
-      <c r="F41" s="10"/>
+      <c r="F41" s="10">
+        <v>70</v>
+      </c>
       <c r="G41" s="10">
         <v>83</v>
       </c>
       <c r="H41" s="10"/>
-      <c r="I41" s="10">
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10">
+        <v>71.699999999999989</v>
+      </c>
+      <c r="M41" s="2">
+        <f t="shared" si="1"/>
+        <v>71.699999999999989</v>
+      </c>
+      <c r="N41" s="2">
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="J41" s="10">
+      <c r="O41" s="2">
+        <v>46</v>
+      </c>
+      <c r="P41" s="2">
         <v>0</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-    </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q41" s="2">
+        <f t="shared" si="0"/>
+        <v>69.459999999999994</v>
+      </c>
+      <c r="R41" s="2">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7" t="s">
         <v>133</v>
       </c>
@@ -2922,23 +3831,46 @@
       <c r="E42" s="10">
         <v>100</v>
       </c>
-      <c r="F42" s="10"/>
+      <c r="F42" s="10">
+        <v>100</v>
+      </c>
       <c r="G42" s="10">
-        <v>83</v>
-      </c>
-      <c r="H42" s="10">
+        <v>100</v>
+      </c>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10">
         <v>1</v>
       </c>
-      <c r="I42" s="10">
+      <c r="K42" s="10">
+        <v>5</v>
+      </c>
+      <c r="L42" s="10">
+        <v>100</v>
+      </c>
+      <c r="M42" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="N42" s="2">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+      <c r="O42" s="2">
         <v>86</v>
       </c>
-      <c r="J42" s="10">
+      <c r="P42" s="2">
         <v>98</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-    </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q42" s="2">
+        <f t="shared" si="0"/>
+        <v>87.75</v>
+      </c>
+      <c r="R42" s="2">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7" t="s">
         <v>136</v>
       </c>
@@ -2952,51 +3884,95 @@
       <c r="E43" s="10">
         <v>100</v>
       </c>
-      <c r="F43" s="10"/>
+      <c r="F43" s="10">
+        <v>100</v>
+      </c>
       <c r="G43" s="10">
-        <v>83</v>
-      </c>
-      <c r="H43" s="10">
+        <v>100</v>
+      </c>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10">
         <v>2</v>
       </c>
-      <c r="I43" s="10">
+      <c r="K43" s="10">
+        <v>5</v>
+      </c>
+      <c r="L43" s="10">
+        <v>100</v>
+      </c>
+      <c r="M43" s="2">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="N43" s="2">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="O43" s="2">
         <v>80</v>
       </c>
-      <c r="J43" s="10">
+      <c r="P43" s="2">
         <v>96</v>
       </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-    </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q43" s="2">
+        <f t="shared" si="0"/>
+        <v>72.349999999999994</v>
+      </c>
+      <c r="R43" s="2">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="26" t="s">
         <v>140</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>141</v>
       </c>
       <c r="D44" s="10"/>
-      <c r="E44" s="10">
+      <c r="E44" s="33">
         <v>44</v>
       </c>
-      <c r="F44" s="10"/>
+      <c r="F44" s="10">
+        <v>80</v>
+      </c>
       <c r="G44" s="10">
         <v>83</v>
       </c>
       <c r="H44" s="10"/>
-      <c r="I44" s="10">
+      <c r="I44" s="10"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10">
+        <v>69.800000000000011</v>
+      </c>
+      <c r="M44" s="2">
+        <f t="shared" si="1"/>
+        <v>69.800000000000011</v>
+      </c>
+      <c r="N44" s="2">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="J44" s="50">
+      <c r="O44" s="2">
+        <v>20</v>
+      </c>
+      <c r="P44" s="41">
         <v>0</v>
       </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-    </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q44" s="2">
+        <f t="shared" si="0"/>
+        <v>61.19</v>
+      </c>
+      <c r="R44" s="2">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="7" t="s">
         <v>142</v>
       </c>
@@ -3010,23 +3986,44 @@
       <c r="E45" s="10">
         <v>89</v>
       </c>
-      <c r="F45" s="10"/>
+      <c r="F45" s="10">
+        <v>100</v>
+      </c>
       <c r="G45" s="10">
-        <v>83</v>
-      </c>
-      <c r="H45" s="10">
+        <v>100</v>
+      </c>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10">
         <v>2</v>
       </c>
-      <c r="I45" s="10">
+      <c r="K45" s="10"/>
+      <c r="L45" s="10">
+        <v>98.7</v>
+      </c>
+      <c r="M45" s="2">
+        <f t="shared" si="1"/>
+        <v>98.7</v>
+      </c>
+      <c r="N45" s="2">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="O45" s="2">
         <v>78</v>
       </c>
-      <c r="J45" s="10">
+      <c r="P45" s="2">
         <v>98</v>
       </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-    </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q45" s="2">
+        <f t="shared" si="0"/>
+        <v>82.46</v>
+      </c>
+      <c r="R45" s="2">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7" t="s">
         <v>145</v>
       </c>
@@ -3040,23 +4037,46 @@
       <c r="E46" s="10">
         <v>100</v>
       </c>
-      <c r="F46" s="10"/>
+      <c r="F46" s="10">
+        <v>100</v>
+      </c>
       <c r="G46" s="10">
-        <v>83</v>
-      </c>
-      <c r="H46" s="10">
+        <v>100</v>
+      </c>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10">
         <v>3</v>
       </c>
-      <c r="I46" s="10">
+      <c r="K46" s="10">
+        <v>5</v>
+      </c>
+      <c r="L46" s="10">
+        <v>100</v>
+      </c>
+      <c r="M46" s="2">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="N46" s="2">
+        <f t="shared" si="2"/>
+        <v>187</v>
+      </c>
+      <c r="O46" s="2">
         <v>90</v>
       </c>
-      <c r="J46" s="10">
+      <c r="P46" s="2">
         <v>97</v>
       </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-    </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q46" s="2">
+        <f t="shared" si="0"/>
+        <v>97.55</v>
+      </c>
+      <c r="R46" s="2">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7" t="s">
         <v>148</v>
       </c>
@@ -3070,49 +4090,91 @@
       <c r="E47" s="10">
         <v>89</v>
       </c>
-      <c r="F47" s="10"/>
+      <c r="F47" s="10">
+        <v>100</v>
+      </c>
       <c r="G47" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H47" s="10"/>
-      <c r="I47" s="10">
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="M47" s="2">
+        <f t="shared" si="1"/>
+        <v>96.7</v>
+      </c>
+      <c r="N47" s="2">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+      <c r="O47" s="2">
         <v>68</v>
       </c>
-      <c r="J47" s="10">
+      <c r="P47" s="2">
         <v>98</v>
       </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q47" s="2">
+        <f t="shared" si="0"/>
+        <v>96.91</v>
+      </c>
+      <c r="R47" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="7" t="s">
         <v>151</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="31" t="s">
         <v>153</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="10">
         <v>78</v>
       </c>
-      <c r="F48" s="10"/>
+      <c r="F48" s="10">
+        <v>100</v>
+      </c>
       <c r="G48" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H48" s="10"/>
-      <c r="I48" s="10">
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10">
+        <v>93.4</v>
+      </c>
+      <c r="M48" s="2">
+        <f t="shared" si="1"/>
+        <v>93.4</v>
+      </c>
+      <c r="N48" s="2">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+      <c r="O48" s="2">
         <v>78</v>
       </c>
-      <c r="J48" s="10">
+      <c r="P48" s="2">
         <v>95</v>
       </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q48" s="2">
+        <f t="shared" si="0"/>
+        <v>54.97</v>
+      </c>
+      <c r="R48" s="29">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7" t="s">
         <v>154</v>
       </c>
@@ -3126,124 +4188,160 @@
       <c r="E49" s="10">
         <v>78</v>
       </c>
-      <c r="F49" s="10"/>
+      <c r="F49" s="10">
+        <v>100</v>
+      </c>
       <c r="G49" s="10">
-        <v>83</v>
-      </c>
-      <c r="H49" s="10">
+        <v>100</v>
+      </c>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10">
         <v>2</v>
       </c>
-      <c r="I49" s="10">
+      <c r="K49" s="10"/>
+      <c r="L49" s="10">
+        <v>95.4</v>
+      </c>
+      <c r="M49" s="2">
+        <f t="shared" si="1"/>
+        <v>95.4</v>
+      </c>
+      <c r="N49" s="2">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+      <c r="O49" s="2">
         <v>38</v>
       </c>
-      <c r="J49" s="10">
-        <v>100</v>
-      </c>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-    </row>
-    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="32" t="s">
+      <c r="P49" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q49" s="2">
+        <f t="shared" si="0"/>
+        <v>72.02</v>
+      </c>
+      <c r="R49" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
-    </row>
-    <row r="52" spans="1:13" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="33" t="s">
+      <c r="B51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="64"/>
+      <c r="F51" s="64"/>
+      <c r="G51" s="64"/>
+      <c r="H51" s="64"/>
+      <c r="I51" s="64"/>
+      <c r="J51" s="64"/>
+      <c r="K51" s="64"/>
+      <c r="L51" s="64"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="64"/>
+      <c r="P51" s="64"/>
+    </row>
+    <row r="52" spans="1:19" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="34" t="s">
+      <c r="B52" s="62"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34" t="s">
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34" t="s">
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="19"/>
-    </row>
-    <row r="53" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="36" t="s">
+      <c r="K52" s="63"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="34"/>
+      <c r="N52" s="34"/>
+      <c r="O52" s="34"/>
+      <c r="P52" s="40"/>
+    </row>
+    <row r="53" spans="1:19" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="39" t="s">
+      <c r="B53" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="40" t="s">
+      <c r="C53" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="38" t="s">
+      <c r="D53" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="35" t="s">
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="58"/>
+      <c r="I53" s="58"/>
+      <c r="J53" s="58"/>
+      <c r="K53" s="58"/>
+      <c r="L53" s="52" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="36"/>
-      <c r="B54" s="39"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="31" t="s">
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+    </row>
+    <row r="54" spans="1:19" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="59"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="61"/>
+      <c r="D54" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="31" t="s">
+      <c r="E54" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="31" t="s">
+      <c r="F54" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="31" t="s">
+      <c r="G54" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="31"/>
-      <c r="L54" s="35"/>
-    </row>
-    <row r="55" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="36"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="35"/>
-    </row>
-    <row r="56" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H54" s="51"/>
+      <c r="I54" s="51"/>
+      <c r="J54" s="51"/>
+      <c r="K54" s="51"/>
+      <c r="L54" s="52"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+    </row>
+    <row r="55" spans="1:19" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="59"/>
+      <c r="B55" s="60"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="36"/>
+      <c r="N55" s="36"/>
+      <c r="O55" s="36"/>
+    </row>
+    <row r="56" spans="1:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="7" t="s">
         <v>157</v>
       </c>
@@ -3257,122 +4355,202 @@
       <c r="E56" s="10">
         <v>89</v>
       </c>
-      <c r="F56" s="10"/>
+      <c r="F56" s="10">
+        <v>100</v>
+      </c>
       <c r="G56" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H56" s="10"/>
-      <c r="I56" s="10">
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="M56" s="2">
+        <f>E56*0.3+F56*0.5+G56*0.2+J56+K56</f>
+        <v>96.7</v>
+      </c>
+      <c r="N56" s="2">
+        <f>O56+P56</f>
+        <v>159</v>
+      </c>
+      <c r="O56" s="2">
         <v>62</v>
       </c>
-      <c r="J56" s="10">
+      <c r="P56" s="2">
         <v>97</v>
       </c>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-    </row>
-    <row r="57" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="7" t="s">
+      <c r="Q56" s="2">
+        <f>L56*0.3+R56*0.7</f>
+        <v>92.359999999999985</v>
+      </c>
+      <c r="R56" s="2">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D57" s="10"/>
+      <c r="D57" s="33"/>
       <c r="E57" s="10">
         <v>89</v>
       </c>
-      <c r="F57" s="10"/>
+      <c r="F57" s="10">
+        <v>100</v>
+      </c>
       <c r="G57" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H57" s="10"/>
-      <c r="I57" s="10">
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="M57" s="2">
+        <f t="shared" ref="M57:M58" si="3">E57*0.3+F57*0.5+G57*0.2+J57+K57</f>
+        <v>96.7</v>
+      </c>
+      <c r="N57" s="2">
+        <f t="shared" ref="N57:N58" si="4">O57+P57</f>
+        <v>164</v>
+      </c>
+      <c r="O57" s="2">
         <v>68</v>
       </c>
-      <c r="J57" s="10">
+      <c r="P57" s="2">
         <v>96</v>
       </c>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-    </row>
-    <row r="58" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S57" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="7" t="s">
         <v>163</v>
       </c>
       <c r="B58" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="31" t="s">
         <v>165</v>
       </c>
       <c r="D58" s="10"/>
-      <c r="E58" s="10">
+      <c r="E58" s="25">
         <v>44</v>
       </c>
-      <c r="F58" s="10"/>
+      <c r="F58" s="10">
+        <v>78</v>
+      </c>
       <c r="G58" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H58" s="10"/>
-      <c r="I58" s="10">
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="10">
+        <v>72.2</v>
+      </c>
+      <c r="M58" s="2">
+        <f t="shared" si="3"/>
+        <v>72.2</v>
+      </c>
+      <c r="N58" s="2">
+        <f t="shared" si="4"/>
+        <v>113</v>
+      </c>
+      <c r="O58" s="2">
         <v>22</v>
       </c>
-      <c r="J58" s="10">
+      <c r="P58" s="2">
         <v>91</v>
       </c>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-    </row>
-    <row r="59" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q58" s="41">
+        <f t="shared" ref="Q58:Q59" si="5">L58*0.3+R58*0.7</f>
+        <v>50.36</v>
+      </c>
+      <c r="R58" s="29">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="31" t="s">
         <v>168</v>
       </c>
       <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-    </row>
-    <row r="60" spans="1:13" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
+      <c r="E59" s="33">
+        <v>60</v>
+      </c>
+      <c r="F59" s="33">
+        <v>60</v>
+      </c>
+      <c r="G59" s="33">
+        <v>60</v>
+      </c>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33">
+        <v>60</v>
+      </c>
+      <c r="M59" s="29"/>
+      <c r="N59" s="29"/>
+      <c r="O59" s="29"/>
+      <c r="Q59" s="41">
+        <f t="shared" si="5"/>
+        <v>55.099999999999994</v>
+      </c>
+      <c r="R59" s="41">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="B60" s="11"/>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A61" s="45" t="s">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A61" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B61" s="45"/>
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45"/>
-      <c r="L61" s="45"/>
-      <c r="M61" s="20"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A62" s="46" t="s">
+      <c r="B61" s="53"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="53"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="53"/>
+      <c r="M61" s="35"/>
+      <c r="N61" s="35"/>
+      <c r="O61" s="35"/>
+      <c r="P61" s="42"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A62" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="47"/>
+      <c r="B62" s="55"/>
       <c r="C62" s="6" t="s">
         <v>12</v>
       </c>
@@ -3388,37 +4566,43 @@
       <c r="G62" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H62" s="46" t="s">
+      <c r="H62" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I62" s="48"/>
-      <c r="J62" s="47"/>
-      <c r="K62" s="49" t="s">
+      <c r="I62" s="56"/>
+      <c r="J62" s="55"/>
+      <c r="K62" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="L62" s="49"/>
-      <c r="M62" s="21"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A63" s="41"/>
-      <c r="B63" s="41"/>
+      <c r="L62" s="57"/>
+      <c r="M62" s="37"/>
+      <c r="N62" s="37"/>
+      <c r="O62" s="37"/>
+      <c r="P62" s="43"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A63" s="47"/>
+      <c r="B63" s="47"/>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
       <c r="E63" s="13"/>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="43"/>
-      <c r="J63" s="44"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="41"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B64" s="24"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="26"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="H63" s="48"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="50"/>
+      <c r="K63" s="47"/>
+      <c r="L63" s="47"/>
+      <c r="M63" s="38"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="38"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B64" s="20"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="22"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B66" s="15" t="s">
         <v>19</v>
       </c>
@@ -3429,13 +4613,42 @@
       </c>
       <c r="H66" s="18"/>
       <c r="J66" s="17"/>
-      <c r="K66" s="22"/>
-      <c r="L66" s="22"/>
-      <c r="M66" s="23"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="H63:J63"/>
     <mergeCell ref="K63:L63"/>
@@ -3451,35 +4664,14 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="D54:D55"/>
-    <mergeCell ref="C3:C5"/>
     <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D3:K3"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
+  <conditionalFormatting sqref="Q6:Q49">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.10972222222222222" right="0.10972222222222222" top="0.38124999999999998" bottom="0.5" header="0.38124999999999998" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <rowBreaks count="1" manualBreakCount="1">

--- a/network/file/成绩登分册-4.xlsx
+++ b/network/file/成绩登分册-4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\network\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF21A86-A014-4C8A-9C79-719F378542DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6AA179-2C06-4632-9890-BFAB87075E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1D86DE0-A88D-486A-A312-07EB4B609A42}"/>
   </bookViews>
@@ -1441,6 +1441,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1453,12 +1486,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1473,33 +1500,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1925,72 +1925,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
       <c r="M1" s="46"/>
       <c r="N1" s="46"/>
       <c r="O1" s="46"/>
       <c r="P1" s="46"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63" t="s">
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63" t="s">
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
       <c r="M2" s="34"/>
       <c r="N2" s="34"/>
       <c r="O2" s="34"/>
       <c r="P2" s="40"/>
     </row>
     <row r="3" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="52" t="s">
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="54" t="s">
         <v>5</v>
       </c>
       <c r="M3" s="36"/>
@@ -2004,47 +2004,47 @@
       </c>
     </row>
     <row r="4" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="51" t="s">
+      <c r="A4" s="50"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="59" t="s">
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="K4" s="51" t="s">
+      <c r="K4" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="L4" s="52"/>
+      <c r="L4" s="54"/>
       <c r="M4" s="36"/>
       <c r="N4" s="36"/>
       <c r="O4" s="36"/>
     </row>
     <row r="5" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="59"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="52"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="54"/>
       <c r="M5" s="36"/>
       <c r="N5" s="36"/>
       <c r="O5" s="36"/>
@@ -2400,7 +2400,7 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="66">
+      <c r="L13" s="47">
         <v>75</v>
       </c>
       <c r="M13" s="2">
@@ -4227,72 +4227,72 @@
     </row>
     <row r="50" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="51" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="64" t="s">
+      <c r="A51" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="64"/>
-      <c r="C51" s="64"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="64"/>
-      <c r="F51" s="64"/>
-      <c r="G51" s="64"/>
-      <c r="H51" s="64"/>
-      <c r="I51" s="64"/>
-      <c r="J51" s="64"/>
-      <c r="K51" s="64"/>
-      <c r="L51" s="64"/>
-      <c r="M51" s="64"/>
-      <c r="N51" s="64"/>
-      <c r="O51" s="64"/>
-      <c r="P51" s="64"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="51"/>
+      <c r="K51" s="51"/>
+      <c r="L51" s="51"/>
+      <c r="M51" s="51"/>
+      <c r="N51" s="51"/>
+      <c r="O51" s="51"/>
+      <c r="P51" s="51"/>
     </row>
     <row r="52" spans="1:19" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="62" t="s">
+      <c r="A52" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="62"/>
-      <c r="C52" s="62"/>
-      <c r="D52" s="63" t="s">
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="63" t="s">
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="63"/>
-      <c r="I52" s="63"/>
-      <c r="J52" s="63" t="s">
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="63"/>
-      <c r="L52" s="63"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="53"/>
       <c r="M52" s="34"/>
       <c r="N52" s="34"/>
       <c r="O52" s="34"/>
       <c r="P52" s="40"/>
     </row>
     <row r="53" spans="1:19" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="59" t="s">
+      <c r="A53" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="61" t="s">
+      <c r="C53" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="58" t="s">
+      <c r="D53" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="58"/>
-      <c r="K53" s="58"/>
-      <c r="L53" s="52" t="s">
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="L53" s="54" t="s">
         <v>5</v>
       </c>
       <c r="M53" s="36"/>
@@ -4300,43 +4300,43 @@
       <c r="O53" s="36"/>
     </row>
     <row r="54" spans="1:19" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="59"/>
-      <c r="B54" s="60"/>
-      <c r="C54" s="61"/>
-      <c r="D54" s="51" t="s">
+      <c r="A54" s="50"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="51" t="s">
+      <c r="E54" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="51" t="s">
+      <c r="F54" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="51" t="s">
+      <c r="G54" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="51"/>
-      <c r="I54" s="51"/>
-      <c r="J54" s="51"/>
-      <c r="K54" s="51"/>
-      <c r="L54" s="52"/>
+      <c r="H54" s="48"/>
+      <c r="I54" s="48"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="48"/>
+      <c r="L54" s="54"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
       <c r="O54" s="36"/>
     </row>
     <row r="55" spans="1:19" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="59"/>
-      <c r="B55" s="60"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="51"/>
-      <c r="K55" s="51"/>
-      <c r="L55" s="52"/>
+      <c r="A55" s="50"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
+      <c r="L55" s="54"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="36"/>
@@ -4527,30 +4527,30 @@
       <c r="C60" s="12"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A61" s="53" t="s">
+      <c r="A61" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="B61" s="53"/>
-      <c r="C61" s="53"/>
-      <c r="D61" s="53"/>
-      <c r="E61" s="53"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
-      <c r="H61" s="53"/>
-      <c r="I61" s="53"/>
-      <c r="J61" s="53"/>
-      <c r="K61" s="53"/>
-      <c r="L61" s="53"/>
+      <c r="B61" s="62"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="62"/>
+      <c r="E61" s="62"/>
+      <c r="F61" s="62"/>
+      <c r="G61" s="62"/>
+      <c r="H61" s="62"/>
+      <c r="I61" s="62"/>
+      <c r="J61" s="62"/>
+      <c r="K61" s="62"/>
+      <c r="L61" s="62"/>
       <c r="M61" s="35"/>
       <c r="N61" s="35"/>
       <c r="O61" s="35"/>
       <c r="P61" s="42"/>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="55"/>
+      <c r="B62" s="64"/>
       <c r="C62" s="6" t="s">
         <v>12</v>
       </c>
@@ -4566,33 +4566,33 @@
       <c r="G62" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H62" s="54" t="s">
+      <c r="H62" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="I62" s="56"/>
-      <c r="J62" s="55"/>
-      <c r="K62" s="57" t="s">
+      <c r="I62" s="65"/>
+      <c r="J62" s="64"/>
+      <c r="K62" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="L62" s="57"/>
+      <c r="L62" s="66"/>
       <c r="M62" s="37"/>
       <c r="N62" s="37"/>
       <c r="O62" s="37"/>
       <c r="P62" s="43"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A63" s="47"/>
-      <c r="B63" s="47"/>
+      <c r="A63" s="58"/>
+      <c r="B63" s="58"/>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
       <c r="E63" s="13"/>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="49"/>
-      <c r="J63" s="50"/>
-      <c r="K63" s="47"/>
-      <c r="L63" s="47"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="60"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="58"/>
+      <c r="L63" s="58"/>
       <c r="M63" s="38"/>
       <c r="N63" s="38"/>
       <c r="O63" s="38"/>
@@ -4622,6 +4622,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="L53:L55"/>
+    <mergeCell ref="A61:L61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="D53:K53"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="G54:G55"/>
     <mergeCell ref="H54:H55"/>
     <mergeCell ref="I54:I55"/>
@@ -4638,33 +4665,6 @@
     <mergeCell ref="D3:K3"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="L53:L55"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="D53:K53"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="F54:F55"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="Q6:Q49">
